--- a/LOreal_AI_Discovery_Analysis.xlsx
+++ b/LOreal_AI_Discovery_Analysis.xlsx
@@ -30,7 +30,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="159">
   <si>
-    <t xml:space="preserve">L'Oréal — AI Discovery Measurement Analysis</t>
+    <t xml:space="preserve">L'Oréal: AI Discovery Measurement Analysis</t>
   </si>
   <si>
     <t xml:space="preserve">Portfolio analysis workbook | evidence → calculations → context → charts</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Eurostat isoc_ec_esels.</t>
   </si>
   <si>
-    <t xml:space="preserve">01 — L'Oréal Core Data</t>
+    <t xml:space="preserve">01 · L'Oréal Core Data</t>
   </si>
   <si>
     <t xml:space="preserve">Annual company data | € million unless stated</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">2025: L’Oréal’s Universal Registration Document reports €13.3bn in e-commerce sales, equal to 30.2% of Group sales, up 12.7% in 2025.</t>
   </si>
   <si>
-    <t xml:space="preserve">02 — Calculations</t>
+    <t xml:space="preserve">02 · Calculations</t>
   </si>
   <si>
     <t xml:space="preserve">Formula-driven calculations used in the analysis</t>
@@ -237,7 +237,7 @@
     <t xml:space="preserve">Index interpretation: 2021 is rebased to 100. Indexing shows the full path rather than compressing the period into one CAGR.</t>
   </si>
   <si>
-    <t xml:space="preserve">03 — FRED External Retail Context</t>
+    <t xml:space="preserve">03 · FRED External Retail Context</t>
   </si>
   <si>
     <t xml:space="preserve">U.S. Retail Sales: Health &amp; Personal Care Stores | monthly, seasonally adjusted, $ millions</t>
@@ -264,7 +264,7 @@
     <t xml:space="preserve">Comparability note: FRED is U.S.-only and category-level, while L'Oréal is global and company-specific. Use as directional context only.</t>
   </si>
   <si>
-    <t xml:space="preserve">04 — Eurostat Consumer Adoption</t>
+    <t xml:space="preserve">04 · Eurostat Consumer Adoption</t>
   </si>
   <si>
     <t xml:space="preserve">Last online purchase: in the last 3 months | % of individuals | 2020–2025</t>
@@ -324,10 +324,10 @@
     <t xml:space="preserve">Caveats: this measures people reporting an online purchase in the last 3 months, not beauty purchases or spending. Eurostat flags structural breaks in parts of the series; 2020→2021 comparisons should be treated cautiously. France has no disclosed 2020 value, so its 2020→2021 change is left blank rather than computed against a false zero.</t>
   </si>
   <si>
-    <t xml:space="preserve">05 — Eurostat Business Adoption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enterprises with web sales — B2C | 10 persons employed or more | % of enterprises | 2020–2025</t>
+    <t xml:space="preserve">05 · Eurostat Business Adoption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enterprises with web sales (B2C) | 10 persons employed or more | % of enterprises | 2020–2025</t>
   </si>
   <si>
     <t xml:space="preserve">2024→2025</t>
@@ -336,22 +336,22 @@
     <t xml:space="preserve">Caveats: this is all-sector enterprise adoption, not beauty/retail-specific. France has a flagged break in 2022 in the source series.</t>
   </si>
   <si>
-    <t xml:space="preserve">06 — Chart Source Tables</t>
+    <t xml:space="preserve">06 · Chart Source Tables</t>
   </si>
   <si>
     <t xml:space="preserve">Only the clean tables needed to reproduce the portfolio visuals</t>
   </si>
   <si>
-    <t xml:space="preserve">Chart 1 — E-commerce Share of Sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chart 2 — Growth vs Margin</t>
+    <t xml:space="preserve">Chart 1: E-commerce Share of Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chart 2: Growth vs Margin</t>
   </si>
   <si>
     <t xml:space="preserve">These tables are separated from calculations so the PPT charts can be reproduced without touching the analytical tabs.</t>
   </si>
   <si>
-    <t xml:space="preserve">07 — Sources &amp; Methodology</t>
+    <t xml:space="preserve">07 · Sources &amp; Methodology</t>
   </si>
   <si>
     <t xml:space="preserve">Source audit for the portfolio workbook</t>
@@ -471,13 +471,13 @@
     <t xml:space="preserve">Platform-level geographic targeting and reporting capability</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirms platform capability only — not L'Oréal's specific eligible-market assignment or reporting access.</t>
+    <t xml:space="preserve">Confirms platform capability only, not L'Oréal's specific eligible-market assignment or reporting access.</t>
   </si>
   <si>
     <t xml:space="preserve">Comparability rule: L'Oréal vs itself supports full quantitative analysis. FRED and Eurostat are contextual/descriptive evidence only.</t>
   </si>
   <si>
-    <t xml:space="preserve">08 — Appendix Analysis</t>
+    <t xml:space="preserve">08 · Appendix Analysis</t>
   </si>
   <si>
     <t xml:space="preserve">Supporting observations behind the main portfolio narrative</t>
@@ -492,7 +492,7 @@
     <t xml:space="preserve">Reported growth includes currency/scope effects; LFL growth is based on comparable structure and identical exchange rates. The main deck uses LFL for the five-year operating trend.</t>
   </si>
   <si>
-    <t xml:space="preserve">Spain — 2024→2025 Divergence</t>
+    <t xml:space="preserve">Spain: 2024→2025 Divergence</t>
   </si>
   <si>
     <t xml:space="preserve">Indicator</t>
